--- a/AIVIA_Design/L1_KG1_Technical_Layer_Registry_DRAFT.xlsx
+++ b/AIVIA_Design/L1_KG1_Technical_Layer_Registry_DRAFT.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>grain (pending Sunny's dictionary check) · extract format (the layer's input contract — next design conversation) · containment edge direction (doc says contains parent-&gt;child; the ratified point-toward-stability convention says belongs_to child-&gt;parent — unresolved, see morning report)</t>
+          <t>ALL CLOSED as of 2026-09-05: grain ruled opportunistic (field-calibrated); extract format = CONTRACT_DATALOAD (complete, v0.1 file format pinned by F1); containment direction ratified (references point toward stability, containment parent-&gt;child).</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1223,6 +1223,33 @@
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>to build</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>registration prerequisite (A1 refined 2026-09-05)</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>INTAKE-8 unregistered-db refusal; INTAKE-9 declared-vs-captured db agreement</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>the db is a DBA-completed prereq, never extract-derived; extracts attach schemas downward into a pre-registered db only; the dba responsibility mints from the prereq</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>F1 (registration.json; both snapshots pass); an unregistered-db refusal case (fixture to author)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>to build</t>
         </is>

--- a/AIVIA_Design/L1_KG1_Technical_Layer_Registry_DRAFT.xlsx
+++ b/AIVIA_Design/L1_KG1_Technical_Layer_Registry_DRAFT.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>enum: epic | erp | org | ...</t>
+          <t>registered source system; declared in the registration prereq's SCHEMA MAPPING, never extracted; since A2 the first component of identity — never stored as a second field</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">

--- a/AIVIA_Design/L1_KG1_Technical_Layer_Registry_DRAFT.xlsx
+++ b/AIVIA_Design/L1_KG1_Technical_Layer_Registry_DRAFT.xlsx
@@ -721,17 +721,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>when declared</t>
+          <t>yes (INTAKE-10 guarantees)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>ORDERED list of column names</t>
+          <t>ORDERED list, loaded from the source's declared pk metadata</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>absent =&gt; counted gap list, never guessed; carries the table's grain</t>
+          <t>Sunny's ruling 2026-09-05: declared data, never prose; the phrase rule + gap list retired; referential integrity at intake</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1250,6 +1250,33 @@
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>to build</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>pk integrity (Sunny 2026-09-05)</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>INTAKE-10</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>every extracted table has &gt;=1 declared pk row; violation = named refusal listing keyless tables</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>F1 (all 7 tables carry pk rows); keyless-table refusal fixture (to author, with the unregistered-db one)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>to build</t>
         </is>
